--- a/assets/constructions/examples/ctd_ds1.xlsx
+++ b/assets/constructions/examples/ctd_ds1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,84 +609,113 @@
           <t>hand</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2300-1479-A1 ВК8 ГОСТ 886-77</t>
+          <t>DC20E0460U</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ТИЗ</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>AMATI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DC20</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>SN</t>
-        </is>
-      </c>
+          <t>PMK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="I2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ВК8</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>Super MG</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Super MG</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ГОСТ 886-77</t>
-        </is>
-      </c>
+          <t>TISIN</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>63</v>
-      </c>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="V2" t="n">
-        <v>2.884</v>
+        <v>0.953</v>
       </c>
       <c r="W2" t="n">
-        <v>184</v>
+        <v>150</v>
       </c>
       <c r="X2" t="n">
-        <v>181.116</v>
+        <v>149.047</v>
       </c>
       <c r="Y2" t="n">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -696,23 +725,23 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2019/Каталог высокоточных инструментов</t>
+          <t>2023/Amati Форма Точности</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>BRH</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>m7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>HL-9.6</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -723,54 +752,71 @@
       <c r="AJ2" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>PMK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2300-0053-A1 Р6М5К5 ГОСТ 886-77 с парооксидированием</t>
+          <t>6156-d26.5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ТИЗ</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>ILIX</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6156</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PKN</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KN</t>
+          <t>M</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7.7</v>
+        <v>26.5</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>31.625</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Р6М5К5</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>HSS</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>VAP</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ГОСТ 886-77</t>
+          <t>DIN 1897</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -778,31 +824,33 @@
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>7.7</v>
+        <v>26.5</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>HA</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>56</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="U3" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="V3" t="n">
-        <v>2.313</v>
+        <v>6.179</v>
       </c>
       <c r="W3" t="n">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="X3" t="n">
-        <v>162.687</v>
+        <v>149.821</v>
       </c>
       <c r="Y3" t="n">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -812,7 +860,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2019/Каталог высокоточных инструментов</t>
+          <t>2015 / Ilix General Catalog</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -822,13 +870,13 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>h8</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>HA-7.7</t>
+          <t>HA-26.5</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -839,52 +887,57 @@
       <c r="AJ3" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6153-d1.45</t>
+          <t>2300-5701-A1 11Р3М3Ф2 ГОСТ 4010-77</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ILIX</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6153</t>
-        </is>
-      </c>
+          <t>ТИЗ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PKN</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>PMN</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.45</v>
+        <v>15</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>15.463</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10.663</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>HSS-Co</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>11Р3М3Ф2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>NONE</t>
@@ -892,7 +945,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>DIN 338</t>
+          <t>ГОСТ 4010-77</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -900,33 +953,31 @@
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>1.45</v>
+        <v>15</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>HA</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="S4" t="n">
+        <v>55</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="V4" t="n">
-        <v>0.419</v>
+        <v>4.506</v>
       </c>
       <c r="W4" t="n">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="X4" t="n">
-        <v>39.581</v>
+        <v>106.494</v>
       </c>
       <c r="Y4" t="n">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -936,7 +987,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2015 / Ilix General Catalog</t>
+          <t>2019/Каталог высокоточных инструментов</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -946,13 +997,13 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>h8</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>HA-1.45</t>
+          <t>HA-15</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -963,86 +1014,97 @@
       <c r="AJ4" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>PMNS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2300-2524 Р6М5 ГОСТ 10902-77</t>
+          <t>MFE1900X02S200 DP1020</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ТИЗ</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>MITSUBISHI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MFE</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PNK</t>
+          <t>PMK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17.75</v>
+        <v>19</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>42.75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.25</v>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Р6М5</t>
+          <t>DP1020</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>ГОСТ 10902-77</t>
-        </is>
-      </c>
+          <t>DP</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>17.75</v>
+        <v>20</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>61</v>
-      </c>
+          <t>HA</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="V5" t="n">
-        <v>5.333</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="X5" t="n">
-        <v>185.667</v>
+        <v>127</v>
       </c>
       <c r="Y5" t="n">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1052,23 +1114,23 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2019/Каталог высокоточных инструментов</t>
+          <t>2020 \ Mitsubhishi website</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>0/-0,021</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>HL-17.75</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1079,49 +1141,70 @@
       <c r="AJ5" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>PMKN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>122432 9,4</t>
+          <t>DC160-03-11.500A0-WJ30ET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GARANT</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>122432</t>
+          <t>DC160</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>PKNS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MHO</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>h6</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>WJ30ET</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiSiAlCrN / AlTiN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1130,39 +1213,39 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
         <v>140</v>
       </c>
       <c r="V6" t="n">
-        <v>1.711</v>
+        <v>2.09</v>
       </c>
       <c r="W6" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="X6" t="n">
-        <v>87.289</v>
+        <v>99.91</v>
       </c>
       <c r="Y6" t="n">
-        <v>47</v>
-      </c>
-      <c r="Z6" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
@@ -1170,7 +1253,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2020 / hoffmann-group.ru</t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1180,13 +1263,13 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>m6</t>
+          <t>m7</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>HB-10</t>
+          <t>HA-12</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1197,6 +1280,17 @@
       <c r="AJ6" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>PMKNSHO</t>
         </is>
       </c>
     </row>
